--- a/Outputs/Scenarios/PtX_demand_SK_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_SK_Electrification.xlsx
@@ -840,7 +840,7 @@
         <v>0.03388154143360281</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0003041955337624001</v>
+        <v>0.0003041955337624</v>
       </c>
       <c r="H11" t="n">
         <v>0.0018859603843858</v>
@@ -1555,7 +1555,7 @@
         <v>0.0020673772607307</v>
       </c>
       <c r="K30" t="n">
-        <v>0.0001715964151728307</v>
+        <v>0.0001715964151728306</v>
       </c>
     </row>
     <row r="31">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.0001143976101152205</v>
+        <v>0.0001143976101152204</v>
       </c>
     </row>
     <row r="33">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0001715964151728307</v>
+        <v>0.0001715964151728306</v>
       </c>
     </row>
     <row r="34">

--- a/Outputs/Scenarios/PtX_demand_SK_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_SK_Electrification.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.001396519609567323</v>
       </c>
       <c r="K16" t="n">
-        <v>3.141923942482495e-05</v>
+        <v>7.197416870900163e-05</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>5.236539904137492e-06</v>
+        <v>3.084607230385786e-06</v>
       </c>
     </row>
     <row r="18">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>2.094615961654997e-05</v>
+        <v>1.233842892154314e-05</v>
       </c>
     </row>
     <row r="19">
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>3.141923942482495e-05</v>
+        <v>1.233842892154314e-05</v>
       </c>
     </row>
     <row r="20">
@@ -1333,7 +1333,7 @@
         <v>0.0001119173419487328</v>
       </c>
       <c r="K24" t="n">
-        <v>5.759641171121405e-05</v>
+        <v>5.654570615363557e-05</v>
       </c>
     </row>
     <row r="25">
@@ -1370,7 +1370,7 @@
         <v>0.0006774359062697156</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0004117744613840286</v>
+        <v>0.0004042626442032225</v>
       </c>
     </row>
     <row r="26">
@@ -1481,7 +1481,7 @@
         <v>2.012148366262912e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>5.236539904137492e-06</v>
+        <v>3.084607230385786e-06</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.0020673772607307</v>
       </c>
       <c r="K30" t="n">
-        <v>0.0001715964151728306</v>
+        <v>0.0003603524718629444</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>2.859940252880511e-05</v>
+        <v>1.544367736555476e-05</v>
       </c>
     </row>
     <row r="32">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.0001143976101152204</v>
+        <v>6.177470946221906e-05</v>
       </c>
     </row>
     <row r="33">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0001715964151728306</v>
+        <v>6.177470946221906e-05</v>
       </c>
     </row>
     <row r="34">
@@ -1999,7 +1999,7 @@
         <v>0.0001088093295121421</v>
       </c>
       <c r="K42" t="n">
-        <v>2.859940252880511e-05</v>
+        <v>1.544367736555476e-05</v>
       </c>
     </row>
     <row r="43">
